--- a/invigilation_assignments1.xlsx
+++ b/invigilation_assignments1.xlsx
@@ -6204,7 +6204,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N648"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38.84"/>
@@ -6461,7 +6461,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>40</v>
@@ -6502,7 +6502,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>40</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>40</v>
@@ -6584,7 +6584,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>40</v>
@@ -6625,7 +6625,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>40</v>
@@ -6666,7 +6666,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>40</v>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>14</v>
@@ -6748,7 +6748,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>14</v>
@@ -6789,7 +6789,7 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>14</v>
@@ -6830,7 +6830,7 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>14</v>
@@ -6871,7 +6871,7 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>96</v>
@@ -6912,7 +6912,7 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>101</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>101</v>
@@ -6994,7 +6994,7 @@
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>101</v>
@@ -7035,7 +7035,7 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>101</v>
@@ -7076,7 +7076,7 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>101</v>
@@ -7117,7 +7117,7 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>30</v>
@@ -7158,7 +7158,7 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>30</v>
@@ -7199,7 +7199,7 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>30</v>
@@ -7240,7 +7240,7 @@
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>30</v>
@@ -7281,7 +7281,7 @@
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>30</v>
